--- a/output/pdf_financials_xlsx/MPH.xlsx
+++ b/output/pdf_financials_xlsx/MPH.xlsx
@@ -1830,7 +1830,7 @@
         <v>-0.727</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.365</v>
+        <v>-1.365</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>-0.727</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>1.365</v>
+        <v>-1.365</v>
       </c>
       <c r="L99" s="1" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>-0.727</v>
       </c>
       <c r="N175" s="5" t="n">
-        <v>1.365</v>
+        <v>-1.365</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MPH.xlsx
+++ b/output/pdf_financials_xlsx/MPH.xlsx
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.978725</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.371262</v>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.978725</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.371262</v>
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.336609</v>
+        <v>0.357884</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.17628</v>
@@ -7199,7 +7199,7 @@
         <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>-75.181</v>
+        <v>-75.283</v>
       </c>
       <c r="G124" s="3" t="n">
         <v>0</v>
@@ -7247,7 +7247,7 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>-75.181</v>
+        <v>-75.283</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -19225,7 +19225,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -25532,7 +25532,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -29257,7 +29261,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E272" s="5" t="n">

--- a/output/pdf_financials_xlsx/MPH.xlsx
+++ b/output/pdf_financials_xlsx/MPH.xlsx
@@ -6035,40 +6035,40 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>2.574344</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.895826</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.896244</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.878688</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>6.634</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.196</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>1.438</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>2.466</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>2.739</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>1.594</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>1.736</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>1.876</v>
       </c>
       <c r="N100" s="1" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -23675,7 +23675,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -26095,7 +26095,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E232" s="5" t="n">

--- a/output/pdf_financials_xlsx/MPH.xlsx
+++ b/output/pdf_financials_xlsx/MPH.xlsx
@@ -2640,10 +2640,8 @@
       <c r="H37" s="3" t="n">
         <v>10.216</v>
       </c>
-      <c r="I37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="3" t="n">
+        <v>5.097</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>4.659</v>
@@ -4450,7 +4448,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
@@ -4458,16 +4456,16 @@
         </is>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="N70" s="1" t="inlineStr">
         <is>
@@ -4504,7 +4502,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="I71" s="1" t="inlineStr">
         <is>
@@ -4512,16 +4510,16 @@
         </is>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="N71" s="1" t="inlineStr">
         <is>
@@ -4720,7 +4718,7 @@
         <v>2.554</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>2.278</v>
+        <v>2.038</v>
       </c>
       <c r="I75" s="1" t="inlineStr">
         <is>
@@ -4728,16 +4726,16 @@
         </is>
       </c>
       <c r="J75" s="3" t="n">
-        <v>1.844</v>
+        <v>1.464</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>1.262</v>
+        <v>0.916</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.331</v>
+        <v>0.016</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.463</v>
+        <v>0.095</v>
       </c>
       <c r="N75" s="1" t="inlineStr">
         <is>
@@ -4890,16 +4888,16 @@
         </is>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0</v>
+        <v>0.789</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>0.506</v>
       </c>
       <c r="N78" s="1" t="inlineStr">
         <is>
@@ -4944,16 +4942,16 @@
         </is>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0</v>
+        <v>0.789</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0</v>
+        <v>0.229</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>0</v>
+        <v>0.506</v>
       </c>
       <c r="N79" s="1" t="inlineStr">
         <is>
@@ -4991,35 +4989,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H80" s="3" t="n">
+        <v>0.008908024645534854</v>
       </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J80" s="3" t="n">
+        <v>0.06349464993753734</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0.04041894786955487</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.02734217933252915</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.04206372124362306</v>
       </c>
       <c r="N80" s="1" t="inlineStr">
         <is>
@@ -5280,16 +5268,16 @@
         </is>
       </c>
       <c r="J85" s="3" t="n">
-        <v>1.485</v>
+        <v>0.696</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>0.503</v>
+        <v>0</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>0.229</v>
+        <v>0</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>0.506</v>
+        <v>0</v>
       </c>
       <c r="N85" s="1" t="inlineStr">
         <is>
@@ -6803,40 +6791,40 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.57252</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.23499</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.139601</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.042327</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.127</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-1.281</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-13.66</v>
       </c>
       <c r="I116" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.441</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.296</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.27</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.739</v>
       </c>
       <c r="N116" s="1" t="inlineStr">
         <is>
@@ -8926,7 +8914,11 @@
           <t>Current portion of lease obligations 11</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -9076,7 +9068,11 @@
           <t>Lease obligations 11</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -12572,7 +12568,11 @@
           <t>Lease obligations 11</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -15217,7 +15217,11 @@
           <t>Current portion of lease obligation 4</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -20877,7 +20881,11 @@
           <t>Acquisition of intangible assets 8</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -23282,7 +23290,11 @@
           <t>Deferred income tax expense (recovery) 14</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -24722,7 +24734,11 @@
           <t>Acquisition of intangible assets 9</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -26871,7 +26887,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E242" s="5" t="n">
         <v>-0.57252</v>
       </c>
